--- a/tools/importer/reports/import.report.xlsx
+++ b/tools/importer/reports/import.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="169">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,301 +43,310 @@
     <t>about.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs-team","cards-article","gallery"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:23.500Z</t>
+  </si>
+  <si>
+    <t>About — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/about.html</t>
+  </si>
+  <si>
+    <t>adventures.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","featured-article","editorial-index","columns-promo","cards-article"]</t>
+  </si>
+  <si>
+    <t>adventures</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:08.042Z</t>
+  </si>
+  <si>
+    <t>Adventures — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/adventures.html</t>
+  </si>
+  <si>
+    <t>community.report.json</t>
+  </si>
+  <si>
+    <t>["hero","featured-article","featured-article","editorial-index","cards-article","faq-list"]</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:15.806Z</t>
+  </si>
+  <si>
+    <t>Community — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/community.html</t>
+  </si>
+  <si>
+    <t>destinations.report.json</t>
+  </si>
+  <si>
+    <t>["hero","featured-article","cards-article","cards-article","cards-article","cards-article","gallery"]</t>
+  </si>
+  <si>
+    <t>destinations</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:32.944Z</t>
+  </si>
+  <si>
+    <t>Destinations — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/destinations.html</t>
+  </si>
+  <si>
+    <t>expeditions.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","editorial-index","editorial-index","cards-article"]</t>
+  </si>
+  <si>
+    <t>expeditions</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:36.799Z</t>
+  </si>
+  <si>
+    <t>Expeditions — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/expeditions.html</t>
+  </si>
+  <si>
+    <t>faq.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-article","faq-list","faq-list","faq-list","faq-list","faq-list"]</t>
+  </si>
+  <si>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:27.679Z</t>
+  </si>
+  <si>
+    <t>FAQ — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/faq.html</t>
+  </si>
+  <si>
+    <t>field-notes.report.json</t>
+  </si>
+  <si>
+    <t>["hero","featured-article","cards-article"]</t>
+  </si>
+  <si>
+    <t>field-notes</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:12.707Z</t>
+  </si>
+  <si>
+    <t>Field Notes — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/field-notes</t>
+  </si>
+  <si>
+    <t>gear.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","featured-article","editorial-index","columns-promo","gallery"]</t>
+  </si>
+  <si>
+    <t>gear</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:41.484Z</t>
+  </si>
+  <si>
+    <t>Gear — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/gear.html</t>
+  </si>
+  <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs-activity","featured-article","editorial-index","gallery","ticker","faq-list"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:03.613Z</t>
+  </si>
+  <si>
+    <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/index.html</t>
+  </si>
+  <si>
+    <t>sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero","tabs","featured-article","editorial-index","cards-article","gallery"]</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:20.419Z</t>
+  </si>
+  <si>
+    <t>Sustainability — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/sustainability.html</t>
+  </si>
+  <si>
+    <t>blog/alpine-cycling.report.json</t>
+  </si>
+  <si>
+    <t>["hero-article","columns-pullquote","cards-article","gallery"]</t>
+  </si>
+  <si>
+    <t>blog/alpine-cycling</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:54.348Z</t>
+  </si>
+  <si>
+    <t>Six Days Through the High Alps — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/alpine-cycling.html</t>
+  </si>
+  <si>
+    <t>blog/kayaking-norway.report.json</t>
+  </si>
+  <si>
+    <t>blog/kayaking-norway</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:49.074Z</t>
+  </si>
+  <si>
+    <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/kayaking-norway.html</t>
+  </si>
+  <si>
+    <t>blog/mountain-photography.report.json</t>
+  </si>
+  <si>
+    <t>blog/mountain-photography</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:15:02.971Z</t>
+  </si>
+  <si>
+    <t>The Camera on Your Back — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/mountain-photography.html</t>
+  </si>
+  <si>
+    <t>blog/patagonia-trek.report.json</t>
+  </si>
+  <si>
+    <t>blog/patagonia-trek</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:45.280Z</t>
+  </si>
+  <si>
+    <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/patagonia-trek.html</t>
+  </si>
+  <si>
+    <t>blog/ultralight-backpacking.report.json</t>
+  </si>
+  <si>
+    <t>blog/ultralight-backpacking</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:15:07.353Z</t>
+  </si>
+  <si>
+    <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/ultralight-backpacking.html</t>
+  </si>
+  <si>
+    <t>blog/yosemite-rock-climbing.report.json</t>
+  </si>
+  <si>
+    <t>blog/yosemite-rock-climbing</t>
+  </si>
+  <si>
+    <t>2026-04-13T11:14:59.482Z</t>
+  </si>
+  <si>
+    <t>First Light on the Valley — WKND Adventures</t>
+  </si>
+  <si>
+    <t>https://wknd-adventures.com/blog/yosemite-rock-climbing.html</t>
+  </si>
+  <si>
+    <t>wknd/about.report.json</t>
+  </si>
+  <si>
     <t>["hero","tabs-team","columns-about","cards-feature","cards-article"]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:45.001Z</t>
-  </si>
-  <si>
-    <t>About — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/about.html</t>
-  </si>
-  <si>
-    <t>adventures.report.json</t>
+    <t>wknd/about</t>
+  </si>
+  <si>
+    <t>2026-03-26T17:44:33.555Z</t>
+  </si>
+  <si>
+    <t>wknd/adventures.report.json</t>
   </si>
   <si>
     <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-promo","cards-article"]</t>
   </si>
   <si>
-    <t>adventures</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:29.010Z</t>
-  </si>
-  <si>
-    <t>Adventures — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/adventures.html</t>
-  </si>
-  <si>
-    <t>community.report.json</t>
+    <t>wknd/adventures</t>
+  </si>
+  <si>
+    <t>2026-03-26T17:44:14.598Z</t>
+  </si>
+  <si>
+    <t>wknd/community.report.json</t>
   </si>
   <si>
     <t>["hero","columns-featured","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","accordion-faq"]</t>
-  </si>
-  <si>
-    <t>community</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:37.600Z</t>
-  </si>
-  <si>
-    <t>Community — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/community.html</t>
-  </si>
-  <si>
-    <t>destinations.report.json</t>
-  </si>
-  <si>
-    <t>["hero","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
-  </si>
-  <si>
-    <t>destinations</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:53.010Z</t>
-  </si>
-  <si>
-    <t>Destinations — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/destinations.html</t>
-  </si>
-  <si>
-    <t>expeditions.report.json</t>
-  </si>
-  <si>
-    <t>["hero","tabs-activity","columns-numbered","columns-numbered","columns-promo","cards-article"]</t>
-  </si>
-  <si>
-    <t>expeditions</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:57.641Z</t>
-  </si>
-  <si>
-    <t>Expeditions — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/expeditions.html</t>
-  </si>
-  <si>
-    <t>faq.report.json</t>
-  </si>
-  <si>
-    <t>["hero","columns-promo","cards-article","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq"]</t>
-  </si>
-  <si>
-    <t>faq</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:48.724Z</t>
-  </si>
-  <si>
-    <t>Questions — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/faq.html</t>
-  </si>
-  <si>
-    <t>field-notes.report.json</t>
-  </si>
-  <si>
-    <t>["hero","tabs-activity","columns-featured","columns-promo"]</t>
-  </si>
-  <si>
-    <t>field-notes</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:33.925Z</t>
-  </si>
-  <si>
-    <t>Field Notes — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/field-notes</t>
-  </si>
-  <si>
-    <t>gear.report.json</t>
-  </si>
-  <si>
-    <t>["hero","tabs-activity","tabs","columns-featured","columns-numbered","cards-feature"]</t>
-  </si>
-  <si>
-    <t>gear</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:00.947Z</t>
-  </si>
-  <si>
-    <t>Gear — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/gear.html</t>
-  </si>
-  <si>
-    <t>index.report.json</t>
-  </si>
-  <si>
-    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-gallery","ticker","accordion-faq"]</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:25.619Z</t>
-  </si>
-  <si>
-    <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/index.html</t>
-  </si>
-  <si>
-    <t>sustainability.report.json</t>
-  </si>
-  <si>
-    <t>["hero","tabs","columns-featured","columns-numbered","columns-about","cards-feature","cards-article"]</t>
-  </si>
-  <si>
-    <t>sustainability</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:54:41.309Z</t>
-  </si>
-  <si>
-    <t>Wild Ethics — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/sustainability.html</t>
-  </si>
-  <si>
-    <t>blog/alpine-cycling.report.json</t>
-  </si>
-  <si>
-    <t>["hero-article","columns-sidebar","cards-article","columns-gallery"]</t>
-  </si>
-  <si>
-    <t>blog/alpine-cycling</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:15.057Z</t>
-  </si>
-  <si>
-    <t>Six Days Through the High Alps — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/alpine-cycling.html</t>
-  </si>
-  <si>
-    <t>blog/kayaking-norway.report.json</t>
-  </si>
-  <si>
-    <t>blog/kayaking-norway</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:10.833Z</t>
-  </si>
-  <si>
-    <t>Lofoten Islands: Arctic Surfing at the Top of the World — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/kayaking-norway.html</t>
-  </si>
-  <si>
-    <t>blog/mountain-photography.report.json</t>
-  </si>
-  <si>
-    <t>blog/mountain-photography</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:25.211Z</t>
-  </si>
-  <si>
-    <t>The Camera on Your Back — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/mountain-photography.html</t>
-  </si>
-  <si>
-    <t>blog/patagonia-trek.report.json</t>
-  </si>
-  <si>
-    <t>blog/patagonia-trek</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:05.152Z</t>
-  </si>
-  <si>
-    <t>W Circuit: 9 Days, 115 km — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/patagonia-trek.html</t>
-  </si>
-  <si>
-    <t>blog/ultralight-backpacking.report.json</t>
-  </si>
-  <si>
-    <t>blog/ultralight-backpacking</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:29.448Z</t>
-  </si>
-  <si>
-    <t>Sub-10 lb: What to Cut, What to Keep — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/ultralight-backpacking.html</t>
-  </si>
-  <si>
-    <t>blog/yosemite-rock-climbing.report.json</t>
-  </si>
-  <si>
-    <t>blog/yosemite-rock-climbing</t>
-  </si>
-  <si>
-    <t>2026-04-12T18:55:20.336Z</t>
-  </si>
-  <si>
-    <t>First Light on the Valley — WKND Adventures</t>
-  </si>
-  <si>
-    <t>https://wknd-adventures.com/blog/yosemite-rock-climbing.html</t>
-  </si>
-  <si>
-    <t>wknd/about.report.json</t>
-  </si>
-  <si>
-    <t>wknd/about</t>
-  </si>
-  <si>
-    <t>2026-03-26T17:44:33.555Z</t>
-  </si>
-  <si>
-    <t>wknd/adventures.report.json</t>
-  </si>
-  <si>
-    <t>wknd/adventures</t>
-  </si>
-  <si>
-    <t>2026-03-26T17:44:14.598Z</t>
-  </si>
-  <si>
-    <t>wknd/community.report.json</t>
   </si>
   <si>
     <t>wknd/community</t>
@@ -369,6 +378,9 @@
     <t>wknd/destinations.report.json</t>
   </si>
   <si>
+    <t>["hero","columns-featured","columns-numbered","columns-promo","cards-article","cards-article","cards-article","cards-article","cards-article"]</t>
+  </si>
+  <si>
     <t>wknd/destinations</t>
   </si>
   <si>
@@ -378,6 +390,9 @@
     <t>wknd/expeditions.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs-activity","columns-numbered","columns-numbered","columns-promo","cards-article"]</t>
+  </si>
+  <si>
     <t>wknd/expeditions</t>
   </si>
   <si>
@@ -387,15 +402,24 @@
     <t>wknd/faq.report.json</t>
   </si>
   <si>
+    <t>["hero","columns-promo","cards-article","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq"]</t>
+  </si>
+  <si>
     <t>wknd/faq</t>
   </si>
   <si>
     <t>2026-03-26T17:44:37.734Z</t>
   </si>
   <si>
+    <t>Questions — WKND Adventures</t>
+  </si>
+  <si>
     <t>wknd/field-notes.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs-activity","columns-featured","columns-promo"]</t>
+  </si>
+  <si>
     <t>wknd/field-notes</t>
   </si>
   <si>
@@ -405,6 +429,9 @@
     <t>wknd/gear.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs-activity","tabs","columns-featured","columns-numbered","cards-feature"]</t>
+  </si>
+  <si>
     <t>wknd/gear</t>
   </si>
   <si>
@@ -414,6 +441,9 @@
     <t>wknd/index.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs-activity","columns-featured","columns-numbered","columns-gallery","ticker","accordion-faq"]</t>
+  </si>
+  <si>
     <t>wknd/index</t>
   </si>
   <si>
@@ -423,13 +453,22 @@
     <t>wknd/sustainability.report.json</t>
   </si>
   <si>
+    <t>["hero","tabs","columns-featured","columns-numbered","columns-about","cards-feature","cards-article"]</t>
+  </si>
+  <si>
     <t>wknd/sustainability</t>
   </si>
   <si>
     <t>2026-03-26T17:44:28.745Z</t>
   </si>
   <si>
+    <t>Wild Ethics — WKND Adventures</t>
+  </si>
+  <si>
     <t>wknd/blog/alpine-cycling.report.json</t>
+  </si>
+  <si>
+    <t>["hero-article","columns-sidebar","cards-article","columns-gallery"]</t>
   </si>
   <si>
     <t>wknd/blog/alpine-cycling</t>
@@ -1377,7 +1416,7 @@
         <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1386,13 +1425,13 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -1403,10 +1442,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1415,13 +1454,13 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H19" t="s">
         <v>21</v>
@@ -1432,10 +1471,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -1444,13 +1483,13 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
         <v>27</v>
@@ -1461,25 +1500,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1490,10 +1529,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -1502,13 +1541,13 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H22" t="s">
         <v>33</v>
@@ -1519,10 +1558,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -1531,13 +1570,13 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
         <v>39</v>
@@ -1548,10 +1587,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -1560,16 +1599,16 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="I24" t="s">
         <v>46</v>
@@ -1577,10 +1616,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -1589,13 +1628,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H25" t="s">
         <v>51</v>
@@ -1606,10 +1645,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1618,13 +1657,13 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H26" t="s">
         <v>57</v>
@@ -1635,10 +1674,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1647,13 +1686,13 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H27" t="s">
         <v>63</v>
@@ -1664,10 +1703,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1676,16 +1715,16 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H28" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s">
         <v>70</v>
@@ -1693,10 +1732,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1705,13 +1744,13 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="H29" t="s">
         <v>75</v>
@@ -1722,10 +1761,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1734,13 +1773,13 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="H30" t="s">
         <v>80</v>
@@ -1751,10 +1790,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1763,13 +1802,13 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="H31" t="s">
         <v>85</v>
@@ -1780,10 +1819,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1792,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="H32" t="s">
         <v>90</v>
@@ -1809,10 +1848,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
@@ -1821,13 +1860,13 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H33" t="s">
         <v>95</v>
@@ -1838,10 +1877,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
@@ -1850,13 +1889,13 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="H34" t="s">
         <v>100</v>
